--- a/SoRoSim Robots/my_robot(1.75)(3tendon)/10-09-2025/Validation(1.75)(3tendon).xlsx
+++ b/SoRoSim Robots/my_robot(1.75)(3tendon)/10-09-2025/Validation(1.75)(3tendon).xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://djpropertycom-my.sharepoint.com/personal/noah_familiajones_org/Documents/Work and Projects/Github/Whisker_Inspired_Sensing_CR/SoRoSim Robots/my_robot(1.75)(3tendon)/10-09-2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1923" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC87FC4-C2F3-4838-A404-7139839CC935}"/>
+  <xr:revisionPtr revIDLastSave="1924" documentId="8_{DFFD6B0C-681F-42C8-B2E4-5D4B90AAE966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3982547E-1568-466F-AFB5-6529E785BA1B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="3" xr2:uid="{3D16C37F-3C74-4527-A308-796C339DFE9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Proximal Validation (prelim)" sheetId="1" r:id="rId1"/>
     <sheet name="Distal Validation (prelim)" sheetId="3" r:id="rId2"/>
     <sheet name="Proximal Validation (single)" sheetId="8" r:id="rId3"/>
     <sheet name="Distal Validation (single)" sheetId="9" r:id="rId4"/>
-    <sheet name="Conversion" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId5"/>
+    <sheet name="Conversion" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Distal Validation (prelim)'!$A$3:$V$23</definedName>
@@ -538,7 +539,7 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -564,6 +565,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="11" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -630,6 +636,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -645,15 +654,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="11" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -2629,6 +2629,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2947,37 +2951,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E25416C8-6FFA-4564-9592-20AD22887E1B}">
   <dimension ref="A1:AJ26"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="7" width="9.28515625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="27" width="9.28515625" style="3" customWidth="1"/>
+    <col min="1" max="7" width="9.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="27" width="9.26953125" style="3" customWidth="1"/>
     <col min="28" max="16384" width="8" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
+    <row r="1" spans="1:36" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
@@ -2985,44 +2989,44 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.4">
+      <c r="A2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="27" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="28"/>
-      <c r="J2" s="18" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="20" t="s">
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="24" t="s">
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="26"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="31"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
@@ -3033,7 +3037,7 @@
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -3125,7 +3129,7 @@
       <c r="AI3" s="4"/>
       <c r="AJ3" s="4"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>0.71299999999999997</v>
       </c>
@@ -3216,7 +3220,7 @@
         <v>1.5400774131774986E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>0.42</v>
       </c>
@@ -3307,7 +3311,7 @@
         <v>9.1005441219330019E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>0.85199999999999998</v>
       </c>
@@ -3398,7 +3402,7 @@
         <v>8.4171176227569977E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>0.61099999999999999</v>
       </c>
@@ -3489,7 +3493,7 @@
         <v>2.3977091327667011E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>0.65800000000000003</v>
       </c>
@@ -3580,7 +3584,7 @@
         <v>1.7375508050919031E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>0.36299999999999999</v>
       </c>
@@ -3671,7 +3675,7 @@
         <v>0.12846996016502402</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>0.216</v>
       </c>
@@ -3762,7 +3766,7 @@
         <v>1.3460827956200017E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>0.16600000000000001</v>
       </c>
@@ -3853,7 +3857,7 @@
         <v>3.1191953518391005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>0.184</v>
       </c>
@@ -3944,7 +3948,7 @@
         <v>7.7422694907188408E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>0.96099999999999997</v>
       </c>
@@ -4035,7 +4039,7 @@
         <v>2.366175561904893E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>0.51</v>
       </c>
@@ -4126,7 +4130,7 @@
         <v>5.799335741043099E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>0.309</v>
       </c>
@@ -4217,7 +4221,7 @@
         <v>0.10769937777519203</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>0.89700000000000002</v>
       </c>
@@ -4308,7 +4312,7 @@
         <v>6.5359246330261023E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>0.20399999999999999</v>
       </c>
@@ -4399,7 +4403,7 @@
         <v>5.8712187013625988E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>0.42899999999999999</v>
       </c>
@@ -4490,7 +4494,7 @@
         <v>8.831579915523502E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4522,7 +4526,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -4551,7 +4555,7 @@
       <c r="Z20" s="10"/>
       <c r="AA20" s="10"/>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -4580,7 +4584,7 @@
       <c r="Z21" s="10"/>
       <c r="AA21" s="10"/>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -4609,7 +4613,7 @@
       <c r="Z22" s="10"/>
       <c r="AA22" s="10"/>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -4638,7 +4642,7 @@
       <c r="Z23" s="10"/>
       <c r="AA23" s="10"/>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.4">
       <c r="P26" s="3">
         <v>1.7147952457889899E-3</v>
       </c>
@@ -4676,90 +4680,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3993EB2-5DD9-4DA0-BCDE-0457543667A5}">
   <dimension ref="A1:AD29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="9" style="3"/>
-    <col min="8" max="8" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="21" width="9" style="3"/>
-    <col min="22" max="22" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="23" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+    <row r="1" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="27" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="28"/>
-      <c r="J2" s="18" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="33" t="s">
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="36" t="s">
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="37"/>
-      <c r="V2" s="38"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="43"/>
       <c r="W2" s="4"/>
-      <c r="X2" s="30" t="s">
+      <c r="X2" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="31" t="s">
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
       <c r="AD2" s="5"/>
     </row>
-    <row r="3" spans="1:30" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="32" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -4847,7 +4851,7 @@
       </c>
       <c r="AD3" s="4"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <f>'Proximal Validation (prelim)'!A4</f>
         <v>0.71299999999999997</v>
@@ -4957,7 +4961,7 @@
         <v>0.99992013741094088</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <f>'Proximal Validation (prelim)'!A5</f>
         <v>0.42</v>
@@ -5067,7 +5071,7 @@
         <v>0.9999999999999466</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <f>'Proximal Validation (prelim)'!A6</f>
         <v>0.85199999999999998</v>
@@ -5177,7 +5181,7 @@
         <v>0.707719461487616</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <f>'Proximal Validation (prelim)'!A7</f>
         <v>0.61099999999999999</v>
@@ -5287,7 +5291,7 @@
         <v>0.70020885925358134</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <f>'Proximal Validation (prelim)'!A8</f>
         <v>0.65800000000000003</v>
@@ -5397,7 +5401,7 @@
         <v>-0.77168737819401367</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <f>'Proximal Validation (prelim)'!A9</f>
         <v>0.36299999999999999</v>
@@ -5507,7 +5511,7 @@
         <v>-0.59565431770314525</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <f>'Proximal Validation (prelim)'!A10</f>
         <v>0.216</v>
@@ -5617,7 +5621,7 @@
         <v>-0.86204966180318732</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <f>'Proximal Validation (prelim)'!A11</f>
         <v>0.16600000000000001</v>
@@ -5727,7 +5731,7 @@
         <v>-0.82902393856112999</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <f>'Proximal Validation (prelim)'!A12</f>
         <v>0.184</v>
@@ -5837,7 +5841,7 @@
         <v>-0.82588500084426275</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <f>'Proximal Validation (prelim)'!A13</f>
         <v>0.96099999999999997</v>
@@ -5947,7 +5951,7 @@
         <v>-0.82554654904604707</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <f>'Proximal Validation (prelim)'!A14</f>
         <v>0.51</v>
@@ -6057,7 +6061,7 @@
         <v>-0.99884743764863093</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <f>'Proximal Validation (prelim)'!A15</f>
         <v>0.309</v>
@@ -6167,7 +6171,7 @@
         <v>-0.99955909649057262</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <f>'Proximal Validation (prelim)'!A16</f>
         <v>0.89700000000000002</v>
@@ -6277,7 +6281,7 @@
         <v>-0.99999999999325373</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <f>'Proximal Validation (prelim)'!A17</f>
         <v>0.20399999999999999</v>
@@ -6387,7 +6391,7 @@
         <v>-0.99597550074656849</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <f>'Proximal Validation (prelim)'!A18</f>
         <v>0.42899999999999999</v>
@@ -6497,7 +6501,7 @@
         <v>-0.93912340922049664</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -6521,7 +6525,7 @@
       <c r="U19" s="10"/>
       <c r="V19" s="10"/>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -6545,7 +6549,7 @@
       <c r="U20" s="10"/>
       <c r="V20" s="10"/>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -6569,7 +6573,7 @@
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -6593,7 +6597,7 @@
       <c r="U22" s="10"/>
       <c r="V22" s="10"/>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -6617,14 +6621,14 @@
       <c r="U23" s="10"/>
       <c r="V23" s="10"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="T24" s="29" t="s">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="T24" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="U24" s="34"/>
+      <c r="V24" s="34"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.4">
       <c r="T25" s="3" cm="1">
         <f t="array" ref="T25">AVERAGE(ABS(T4:T18))</f>
         <v>8.2714999999999997E-2</v>
@@ -6638,14 +6642,14 @@
         <v>3.4081539627227402</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="T26" s="29" t="s">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="T26" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="U26" s="34"/>
+      <c r="V26" s="34"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.4">
       <c r="T27" s="9">
         <f>AVERAGE(T4:T18)</f>
         <v>-7.2674199999999994E-2</v>
@@ -6659,14 +6663,14 @@
         <v>3.4081539627227402</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="T28" s="29" t="s">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.4">
+      <c r="T28" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="U28" s="34"/>
+      <c r="V28" s="34"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.4">
       <c r="T29" s="3">
         <f>_xlfn.STDEV.S(T4:T18)</f>
         <v>7.9952521667728343E-2</v>
@@ -6703,47 +6707,47 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22B4A24-01F9-43FA-AE7F-5A1710EEAA53}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:25" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="18" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="20" t="s">
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="24" t="s">
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="26"/>
-    </row>
-    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="31"/>
+    </row>
+    <row r="2" spans="1:25" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -6820,1247 +6824,1247 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="45">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="18">
         <v>0.7</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="18">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="18">
         <v>1.571</v>
       </c>
-      <c r="D3" s="45">
+      <c r="D3" s="18">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="18">
         <v>1.4</v>
       </c>
-      <c r="F3" s="45">
-        <v>0</v>
-      </c>
-      <c r="G3" s="45">
-        <v>0</v>
-      </c>
-      <c r="H3" s="47">
+      <c r="F3" s="18">
+        <v>0</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0</v>
+      </c>
+      <c r="H3" s="20">
         <v>6.98671909049153E-4</v>
       </c>
-      <c r="I3" s="47">
+      <c r="I3" s="20">
         <v>-0.12202821671962701</v>
       </c>
-      <c r="J3" s="47">
+      <c r="J3" s="20">
         <v>-3.2366467639803899E-3</v>
       </c>
-      <c r="K3" s="47">
+      <c r="K3" s="20">
         <v>0.37189677357673601</v>
       </c>
-      <c r="L3" s="47">
+      <c r="L3" s="20">
         <v>-5.3712725639343296E-3</v>
       </c>
-      <c r="M3" s="47">
+      <c r="M3" s="20">
         <v>0.55187070369720503</v>
       </c>
-      <c r="N3" s="47">
+      <c r="N3" s="20">
         <v>2.5787867677616715E-3</v>
       </c>
-      <c r="O3" s="47">
+      <c r="O3" s="20">
         <v>-0.13208672274347444</v>
       </c>
-      <c r="P3" s="47">
+      <c r="P3" s="20">
         <v>5.8244073154007812E-3</v>
       </c>
-      <c r="Q3" s="47">
+      <c r="Q3" s="20">
         <v>0.3187407179240575</v>
       </c>
-      <c r="R3" s="47">
+      <c r="R3" s="20">
         <v>3.364049287741272E-2</v>
       </c>
-      <c r="S3" s="47">
+      <c r="S3" s="20">
         <v>0.62230890891075519</v>
       </c>
-      <c r="T3" s="44">
+      <c r="T3" s="17">
         <f t="shared" ref="T3:Y17" si="0">ABS(H3-N3)</f>
         <v>1.8801148587125186E-3</v>
       </c>
-      <c r="U3" s="44">
+      <c r="U3" s="17">
         <f t="shared" si="0"/>
         <v>1.0058506023847433E-2</v>
       </c>
-      <c r="V3" s="44">
+      <c r="V3" s="17">
         <f t="shared" si="0"/>
         <v>9.0610540793811707E-3</v>
       </c>
-      <c r="W3" s="44">
+      <c r="W3" s="17">
         <f t="shared" si="0"/>
         <v>5.3156055652678502E-2</v>
       </c>
-      <c r="X3" s="44">
+      <c r="X3" s="17">
         <f t="shared" si="0"/>
         <v>3.9011765441347046E-2</v>
       </c>
-      <c r="Y3" s="44">
+      <c r="Y3" s="17">
         <f t="shared" si="0"/>
         <v>7.0438205213550154E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="45">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="18">
         <v>0.3</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="18">
         <v>0.06</v>
       </c>
-      <c r="C4" s="45">
+      <c r="C4" s="18">
         <v>1.571</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="18">
         <v>1.571</v>
       </c>
-      <c r="E4" s="45">
-        <v>0</v>
-      </c>
-      <c r="F4" s="45">
-        <v>0</v>
-      </c>
-      <c r="G4" s="45">
-        <v>0</v>
-      </c>
-      <c r="H4" s="47">
+      <c r="E4" s="18">
+        <v>0</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
+        <v>0</v>
+      </c>
+      <c r="H4" s="20">
         <v>-3.4992315340787199E-4</v>
       </c>
-      <c r="I4" s="47">
+      <c r="I4" s="20">
         <v>-4.4687353074550601E-2</v>
       </c>
-      <c r="J4" s="47">
+      <c r="J4" s="20">
         <v>4.3301115510985303E-5</v>
       </c>
-      <c r="K4" s="47">
+      <c r="K4" s="20">
         <v>-1.78173277527094E-3</v>
       </c>
-      <c r="L4" s="47">
+      <c r="L4" s="20">
         <v>3.9914771914482099E-3</v>
       </c>
-      <c r="M4" s="47">
+      <c r="M4" s="20">
         <v>0.286231309175491</v>
       </c>
-      <c r="N4" s="47">
+      <c r="N4" s="20">
         <v>1.494499847778209E-23</v>
       </c>
-      <c r="O4" s="47">
+      <c r="O4" s="20">
         <v>-4.4950326032990831E-2</v>
       </c>
-      <c r="P4" s="47">
+      <c r="P4" s="20">
         <v>-9.1551771001730594E-6</v>
       </c>
-      <c r="Q4" s="47">
+      <c r="Q4" s="20">
         <v>-8.5121069368068528E-3</v>
       </c>
-      <c r="R4" s="47">
+      <c r="R4" s="20">
         <v>-6.1077351384218026E-5</v>
       </c>
-      <c r="S4" s="47">
+      <c r="S4" s="20">
         <v>0.29987916431460937</v>
       </c>
-      <c r="T4" s="44">
+      <c r="T4" s="17">
         <f t="shared" si="0"/>
         <v>3.4992315340787199E-4</v>
       </c>
-      <c r="U4" s="44">
+      <c r="U4" s="17">
         <f t="shared" si="0"/>
         <v>2.6297295844023016E-4</v>
       </c>
-      <c r="V4" s="44">
+      <c r="V4" s="17">
         <f t="shared" si="0"/>
         <v>5.245629261115836E-5</v>
       </c>
-      <c r="W4" s="44">
+      <c r="W4" s="17">
         <f t="shared" si="0"/>
         <v>6.730374161535913E-3</v>
       </c>
-      <c r="X4" s="44">
+      <c r="X4" s="17">
         <f t="shared" si="0"/>
         <v>4.0525545428324282E-3</v>
       </c>
-      <c r="Y4" s="44">
+      <c r="Y4" s="17">
         <f t="shared" si="0"/>
         <v>1.364785513911837E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="45">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="18">
         <v>0.4</v>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="18">
         <v>0.08</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="18">
         <v>2.3559999999999999</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="18">
         <v>0.52400000000000002</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="18">
         <v>1.4</v>
       </c>
-      <c r="F5" s="45">
-        <v>0</v>
-      </c>
-      <c r="G5" s="45">
-        <v>0</v>
-      </c>
-      <c r="H5" s="47">
+      <c r="F5" s="18">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18">
+        <v>0</v>
+      </c>
+      <c r="H5" s="20">
         <v>-1.44779565744102E-4</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="20">
         <v>-2.2709889337420502E-2</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="20">
         <v>-2.47002802789211E-2</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="20">
         <v>0.37153226137161299</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="20">
         <v>-0.145699113607407</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="20">
         <v>0.141014218330383</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="20">
         <v>3.6914386131118719E-4</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="20">
         <v>-2.6089227057806145E-2</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="20">
         <v>-2.3130061105590891E-2</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="20">
         <v>0.3416243160199931</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="20">
         <v>-0.13532486427896148</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="20">
         <v>0.15804753852551109</v>
       </c>
-      <c r="T5" s="44">
+      <c r="T5" s="17">
         <f t="shared" si="0"/>
         <v>5.1392342705528925E-4</v>
       </c>
-      <c r="U5" s="44">
+      <c r="U5" s="17">
         <f t="shared" si="0"/>
         <v>3.3793377203856431E-3</v>
       </c>
-      <c r="V5" s="44">
+      <c r="V5" s="17">
         <f t="shared" si="0"/>
         <v>1.570219173330209E-3</v>
       </c>
-      <c r="W5" s="44">
+      <c r="W5" s="17">
         <f t="shared" si="0"/>
         <v>2.9907945351619891E-2</v>
       </c>
-      <c r="X5" s="44">
+      <c r="X5" s="17">
         <f t="shared" si="0"/>
         <v>1.0374249328445523E-2</v>
       </c>
-      <c r="Y5" s="44">
+      <c r="Y5" s="17">
         <f t="shared" si="0"/>
         <v>1.7033320195128099E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="45">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" s="18">
         <v>0.4</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="18">
         <v>0.2</v>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="18">
         <v>2.3559999999999999</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="18">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E6" s="45">
-        <v>0</v>
-      </c>
-      <c r="F6" s="45">
-        <v>0</v>
-      </c>
-      <c r="G6" s="45">
-        <v>0</v>
-      </c>
-      <c r="H6" s="47">
+      <c r="E6" s="18">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18">
+        <v>0</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0</v>
+      </c>
+      <c r="H6" s="20">
         <v>9.3833426944911494E-5</v>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="20">
         <v>-5.1531359553337097E-2</v>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="20">
         <v>-5.3816821426153197E-2</v>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="20">
         <v>0.240476429462433</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="20">
         <v>-0.18773703277111101</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="20">
         <v>0.19507205486297599</v>
       </c>
-      <c r="N6" s="47">
+      <c r="N6" s="20">
         <v>-2.4396936287641076E-19</v>
       </c>
-      <c r="O6" s="47">
+      <c r="O6" s="20">
         <v>-6.567817720742225E-2</v>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="20">
         <v>-6.5652634652240791E-2</v>
       </c>
-      <c r="Q6" s="47">
+      <c r="Q6" s="20">
         <v>0.18519494211795448</v>
       </c>
-      <c r="R6" s="47">
+      <c r="R6" s="20">
         <v>-0.25065308201113884</v>
       </c>
-      <c r="S6" s="47">
+      <c r="S6" s="20">
         <v>0.25075060011094691</v>
       </c>
-      <c r="T6" s="44">
+      <c r="T6" s="17">
         <f t="shared" si="0"/>
         <v>9.3833426944911737E-5</v>
       </c>
-      <c r="U6" s="44">
+      <c r="U6" s="17">
         <f t="shared" si="0"/>
         <v>1.4146817654085153E-2</v>
       </c>
-      <c r="V6" s="44">
+      <c r="V6" s="17">
         <f t="shared" si="0"/>
         <v>1.1835813226087594E-2</v>
       </c>
-      <c r="W6" s="44">
+      <c r="W6" s="17">
         <f t="shared" si="0"/>
         <v>5.5281487344478519E-2</v>
       </c>
-      <c r="X6" s="44">
+      <c r="X6" s="17">
         <f t="shared" si="0"/>
         <v>6.2916049240027833E-2</v>
       </c>
-      <c r="Y6" s="44">
+      <c r="Y6" s="17">
         <f t="shared" si="0"/>
         <v>5.5678545247970918E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="45">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" s="18">
         <v>0.8</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="18">
         <v>0.1</v>
       </c>
-      <c r="C7" s="45">
+      <c r="C7" s="18">
         <v>2.3559999999999999</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="18">
         <v>1.0469999999999999</v>
       </c>
-      <c r="E7" s="45">
-        <v>0</v>
-      </c>
-      <c r="F7" s="45">
-        <v>0</v>
-      </c>
-      <c r="G7" s="45">
-        <v>0</v>
-      </c>
-      <c r="H7" s="47">
+      <c r="E7" s="18">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0</v>
+      </c>
+      <c r="H7" s="20">
         <v>-4.4502015225589302E-4</v>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="20">
         <v>-0.103923052549362</v>
       </c>
-      <c r="J7" s="47">
+      <c r="J7" s="20">
         <v>-0.113764069974422</v>
       </c>
-      <c r="K7" s="47">
+      <c r="K7" s="20">
         <v>0.34864503145217901</v>
       </c>
-      <c r="L7" s="47">
+      <c r="L7" s="20">
         <v>-0.591894090175629</v>
       </c>
-      <c r="M7" s="47">
+      <c r="M7" s="20">
         <v>0.56364732980728105</v>
       </c>
-      <c r="N7" s="47">
+      <c r="N7" s="20">
         <v>-6.5201141213235506E-19</v>
       </c>
-      <c r="O7" s="47">
+      <c r="O7" s="20">
         <v>-9.8625227823604028E-2</v>
       </c>
-      <c r="P7" s="47">
+      <c r="P7" s="20">
         <v>-9.8586872003892254E-2</v>
       </c>
-      <c r="Q7" s="47">
+      <c r="Q7" s="20">
         <v>0.26552499603872382</v>
       </c>
-      <c r="R7" s="47">
+      <c r="R7" s="20">
         <v>-0.53351334716791143</v>
       </c>
-      <c r="S7" s="47">
+      <c r="S7" s="20">
         <v>0.53372091376721464</v>
       </c>
-      <c r="T7" s="44">
+      <c r="T7" s="17">
         <f t="shared" si="0"/>
         <v>4.4502015225589237E-4</v>
       </c>
-      <c r="U7" s="44">
+      <c r="U7" s="17">
         <f t="shared" si="0"/>
         <v>5.2978247257579741E-3</v>
       </c>
-      <c r="V7" s="44">
+      <c r="V7" s="17">
         <f t="shared" si="0"/>
         <v>1.5177197970529743E-2</v>
       </c>
-      <c r="W7" s="44">
+      <c r="W7" s="17">
         <f t="shared" si="0"/>
         <v>8.3120035413455196E-2</v>
       </c>
-      <c r="X7" s="44">
+      <c r="X7" s="17">
         <f t="shared" si="0"/>
         <v>5.8380743007717562E-2</v>
       </c>
-      <c r="Y7" s="44">
+      <c r="Y7" s="17">
         <f t="shared" si="0"/>
         <v>2.9926416040066406E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="45">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" s="18">
         <v>0.7</v>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="18">
         <v>0.18</v>
       </c>
-      <c r="C8" s="45">
+      <c r="C8" s="18">
         <v>2.3559999999999999</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="18">
         <v>1.0469999999999999</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="18">
         <v>1.4</v>
       </c>
-      <c r="F8" s="45">
-        <v>0</v>
-      </c>
-      <c r="G8" s="45">
-        <v>0</v>
-      </c>
-      <c r="H8" s="47">
+      <c r="F8" s="18">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
+        <v>0</v>
+      </c>
+      <c r="H8" s="20">
         <v>1.9051980000000001E-3</v>
       </c>
-      <c r="I8" s="47">
+      <c r="I8" s="20">
         <v>-0.11076053199999999</v>
       </c>
-      <c r="J8" s="47">
+      <c r="J8" s="20">
         <v>-0.130388632</v>
       </c>
-      <c r="K8" s="47">
+      <c r="K8" s="20">
         <v>0.142369151</v>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="20">
         <v>-0.47970119100000003</v>
       </c>
-      <c r="M8" s="47">
+      <c r="M8" s="20">
         <v>0.43018263600000001</v>
       </c>
-      <c r="N8" s="47">
+      <c r="N8" s="20">
         <v>5.8744905899660044E-3</v>
       </c>
-      <c r="O8" s="47">
+      <c r="O8" s="20">
         <v>-0.13189048818659782</v>
       </c>
-      <c r="P8" s="47">
+      <c r="P8" s="20">
         <v>-0.12217232152508256</v>
       </c>
-      <c r="Q8" s="47">
+      <c r="Q8" s="20">
         <v>6.1072751798252802E-3</v>
       </c>
-      <c r="R8" s="47">
+      <c r="R8" s="20">
         <v>-0.47554113392638969</v>
       </c>
-      <c r="S8" s="47">
+      <c r="S8" s="20">
         <v>0.51363627061923778</v>
       </c>
-      <c r="T8" s="44">
+      <c r="T8" s="17">
         <f t="shared" si="0"/>
         <v>3.9692925899660041E-3</v>
       </c>
-      <c r="U8" s="44">
+      <c r="U8" s="17">
         <f t="shared" si="0"/>
         <v>2.1129956186597826E-2</v>
       </c>
-      <c r="V8" s="44">
+      <c r="V8" s="17">
         <f t="shared" si="0"/>
         <v>8.2163104749174432E-3</v>
       </c>
-      <c r="W8" s="44">
+      <c r="W8" s="17">
         <f t="shared" si="0"/>
         <v>0.13626187582017471</v>
       </c>
-      <c r="X8" s="44">
+      <c r="X8" s="17">
         <f t="shared" si="0"/>
         <v>4.1600570736103348E-3</v>
       </c>
-      <c r="Y8" s="44">
+      <c r="Y8" s="17">
         <f t="shared" si="0"/>
         <v>8.3453634619237771E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="45">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" s="18">
         <v>0.7</v>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="18">
         <v>0.08</v>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="18">
         <v>3.1419999999999999</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="18">
         <v>1.571</v>
       </c>
-      <c r="E9" s="45">
-        <v>0</v>
-      </c>
-      <c r="F9" s="45">
-        <v>0</v>
-      </c>
-      <c r="G9" s="45">
-        <v>0</v>
-      </c>
-      <c r="H9" s="47">
+      <c r="E9" s="18">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18">
+        <v>0</v>
+      </c>
+      <c r="H9" s="20">
         <v>-1.2491350062191499E-3</v>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="20">
         <v>1.1835042387247101E-3</v>
       </c>
-      <c r="J9" s="47">
+      <c r="J9" s="20">
         <v>-0.12853877246379899</v>
       </c>
-      <c r="K9" s="47">
+      <c r="K9" s="20">
         <v>-4.8892773687839501E-2</v>
       </c>
-      <c r="L9" s="47">
+      <c r="L9" s="20">
         <v>-0.72314238548278797</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="20">
         <v>5.8930516242981E-3</v>
       </c>
-      <c r="N9" s="47">
+      <c r="N9" s="20">
         <v>4.5801664250703241E-22</v>
       </c>
-      <c r="O9" s="47">
+      <c r="O9" s="20">
         <v>4.8254721953885884E-5</v>
       </c>
-      <c r="P9" s="47">
+      <c r="P9" s="20">
         <v>-0.11846113793028826</v>
       </c>
-      <c r="Q9" s="47">
+      <c r="Q9" s="20">
         <v>-8.1543560569204657E-2</v>
       </c>
-      <c r="R9" s="47">
+      <c r="R9" s="20">
         <v>-0.69523331610830008</v>
       </c>
-      <c r="S9" s="47">
+      <c r="S9" s="20">
         <v>-2.8320081123673247E-4</v>
       </c>
-      <c r="T9" s="44">
+      <c r="T9" s="17">
         <f t="shared" si="0"/>
         <v>1.2491350062191499E-3</v>
       </c>
-      <c r="U9" s="44">
+      <c r="U9" s="17">
         <f t="shared" si="0"/>
         <v>1.1352495167708241E-3</v>
       </c>
-      <c r="V9" s="44">
+      <c r="V9" s="17">
         <f t="shared" si="0"/>
         <v>1.0077634533510738E-2</v>
       </c>
-      <c r="W9" s="44">
+      <c r="W9" s="17">
         <f t="shared" si="0"/>
         <v>3.2650786881365156E-2</v>
       </c>
-      <c r="X9" s="44">
+      <c r="X9" s="17">
         <f t="shared" si="0"/>
         <v>2.7909069374487894E-2</v>
       </c>
-      <c r="Y9" s="44">
+      <c r="Y9" s="17">
         <f t="shared" si="0"/>
         <v>6.1762524355348323E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="45">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" s="18">
         <v>0.4</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="18">
         <v>0.16</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="18">
         <v>3.1419999999999999</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="18">
         <v>1.571</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="18">
         <v>1.4</v>
       </c>
-      <c r="F10" s="45">
-        <v>0</v>
-      </c>
-      <c r="G10" s="45">
-        <v>0</v>
-      </c>
-      <c r="H10" s="47">
+      <c r="F10" s="18">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0</v>
+      </c>
+      <c r="H10" s="20">
         <v>1.3951195869594799E-3</v>
       </c>
-      <c r="I10" s="47">
+      <c r="I10" s="20">
         <v>3.4124546218663502E-3</v>
       </c>
-      <c r="J10" s="47">
+      <c r="J10" s="20">
         <v>-0.112820729613304</v>
       </c>
-      <c r="K10" s="47">
+      <c r="K10" s="20">
         <v>-4.2202740907669102E-2</v>
       </c>
-      <c r="L10" s="47">
+      <c r="L10" s="20">
         <v>-0.417444437742233</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="20">
         <v>-3.7499666213989301E-3</v>
       </c>
-      <c r="N10" s="47">
+      <c r="N10" s="20">
         <v>1.5142151696091893E-3</v>
       </c>
-      <c r="O10" s="47">
+      <c r="O10" s="20">
         <v>-1.0686885237119154E-5</v>
       </c>
-      <c r="P10" s="47">
+      <c r="P10" s="20">
         <v>-9.9246016845769641E-2</v>
       </c>
-      <c r="Q10" s="47">
+      <c r="Q10" s="20">
         <v>-7.4825408482952618E-2</v>
       </c>
-      <c r="R10" s="47">
+      <c r="R10" s="20">
         <v>-0.39293692809662911</v>
       </c>
-      <c r="S10" s="47">
+      <c r="S10" s="20">
         <v>-1.0993128840352433E-3</v>
       </c>
-      <c r="T10" s="44">
+      <c r="T10" s="17">
         <f t="shared" si="0"/>
         <v>1.1909558264970935E-4</v>
       </c>
-      <c r="U10" s="44">
+      <c r="U10" s="17">
         <f t="shared" si="0"/>
         <v>3.4231415071034692E-3</v>
       </c>
-      <c r="V10" s="44">
+      <c r="V10" s="17">
         <f t="shared" si="0"/>
         <v>1.3574712767534358E-2</v>
       </c>
-      <c r="W10" s="44">
+      <c r="W10" s="17">
         <f t="shared" si="0"/>
         <v>3.2622667575283516E-2</v>
       </c>
-      <c r="X10" s="44">
+      <c r="X10" s="17">
         <f t="shared" si="0"/>
         <v>2.4507509645603887E-2</v>
       </c>
-      <c r="Y10" s="44">
+      <c r="Y10" s="17">
         <f t="shared" si="0"/>
         <v>2.6506537373636868E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="45">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11" s="18">
         <v>0.7</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="18">
         <v>0.18</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="18">
         <v>3.927</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="18">
         <v>0.52400000000000002</v>
       </c>
-      <c r="E11" s="45">
-        <v>0</v>
-      </c>
-      <c r="F11" s="45">
-        <v>0</v>
-      </c>
-      <c r="G11" s="45">
-        <v>0</v>
-      </c>
-      <c r="H11" s="47">
+      <c r="E11" s="18">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20">
         <v>-9.7516691312193898E-5</v>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="20">
         <v>6.3756838440895094E-2</v>
       </c>
-      <c r="J11" s="47">
+      <c r="J11" s="20">
         <v>-6.7828088998794597E-2</v>
       </c>
-      <c r="K11" s="47">
+      <c r="K11" s="20">
         <v>0.525340616703033</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="20">
         <v>-0.27887076139450101</v>
       </c>
-      <c r="M11" s="47">
+      <c r="M11" s="20">
         <v>-0.25877004861831698</v>
       </c>
-      <c r="N11" s="47">
+      <c r="N11" s="20">
         <v>1.2569158172864712E-19</v>
       </c>
-      <c r="O11" s="47">
+      <c r="O11" s="20">
         <v>8.5924146746999081E-2</v>
       </c>
-      <c r="P11" s="47">
+      <c r="P11" s="20">
         <v>-8.5922568676418731E-2</v>
       </c>
-      <c r="Q11" s="47">
+      <c r="Q11" s="20">
         <v>0.46134049280848066</v>
       </c>
-      <c r="R11" s="47">
+      <c r="R11" s="20">
         <v>-0.37226314059225146</v>
       </c>
-      <c r="S11" s="47">
+      <c r="S11" s="20">
         <v>-0.3722699776493763</v>
       </c>
-      <c r="T11" s="44">
+      <c r="T11" s="17">
         <f t="shared" si="0"/>
         <v>9.751669131219402E-5</v>
       </c>
-      <c r="U11" s="44">
+      <c r="U11" s="17">
         <f t="shared" si="0"/>
         <v>2.2167308306103986E-2</v>
       </c>
-      <c r="V11" s="44">
+      <c r="V11" s="17">
         <f t="shared" si="0"/>
         <v>1.8094479677624134E-2</v>
       </c>
-      <c r="W11" s="44">
+      <c r="W11" s="17">
         <f t="shared" si="0"/>
         <v>6.4000123894552341E-2</v>
       </c>
-      <c r="X11" s="44">
+      <c r="X11" s="17">
         <f t="shared" si="0"/>
         <v>9.3392379197750452E-2</v>
       </c>
-      <c r="Y11" s="44">
+      <c r="Y11" s="17">
         <f t="shared" si="0"/>
         <v>0.11349992903105932</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="45">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12" s="18">
         <v>0.3</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="18">
         <v>0.1</v>
       </c>
-      <c r="C12" s="45">
+      <c r="C12" s="18">
         <v>3.927</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="18">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="18">
         <v>1.4</v>
       </c>
-      <c r="F12" s="45">
-        <v>0</v>
-      </c>
-      <c r="G12" s="45">
-        <v>0</v>
-      </c>
-      <c r="H12" s="47">
+      <c r="F12" s="18">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <v>0</v>
+      </c>
+      <c r="H12" s="20">
         <v>-4.7630793415010003E-4</v>
       </c>
-      <c r="I12" s="47">
+      <c r="I12" s="20">
         <v>2.59361006319523E-2</v>
       </c>
-      <c r="J12" s="47">
+      <c r="J12" s="20">
         <v>-2.8502099215984299E-2</v>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="20">
         <v>0.25695684552192699</v>
       </c>
-      <c r="L12" s="47">
+      <c r="L12" s="20">
         <v>-0.14679136872291601</v>
       </c>
-      <c r="M12" s="47">
+      <c r="M12" s="20">
         <v>-0.135155409574509</v>
       </c>
-      <c r="N12" s="47">
+      <c r="N12" s="20">
         <v>-1.6372468824710359E-4</v>
       </c>
-      <c r="O12" s="47">
+      <c r="O12" s="20">
         <v>2.8646764310937781E-2</v>
       </c>
-      <c r="P12" s="47">
+      <c r="P12" s="20">
         <v>-2.7986501267242232E-2</v>
       </c>
-      <c r="Q12" s="47">
+      <c r="Q12" s="20">
         <v>0.21254363126696107</v>
       </c>
-      <c r="R12" s="47">
+      <c r="R12" s="20">
         <v>-0.14733237355599527</v>
       </c>
-      <c r="S12" s="47">
+      <c r="S12" s="20">
         <v>-0.15204563814068989</v>
       </c>
-      <c r="T12" s="44">
+      <c r="T12" s="17">
         <f t="shared" si="0"/>
         <v>3.1258324590299644E-4</v>
       </c>
-      <c r="U12" s="44">
+      <c r="U12" s="17">
         <f t="shared" si="0"/>
         <v>2.710663678985481E-3</v>
       </c>
-      <c r="V12" s="44">
+      <c r="V12" s="17">
         <f t="shared" si="0"/>
         <v>5.1559794874206713E-4</v>
       </c>
-      <c r="W12" s="44">
+      <c r="W12" s="17">
         <f t="shared" si="0"/>
         <v>4.4413214254965916E-2</v>
       </c>
-      <c r="X12" s="44">
+      <c r="X12" s="17">
         <f t="shared" si="0"/>
         <v>5.4100483307925606E-4</v>
       </c>
-      <c r="Y12" s="44">
+      <c r="Y12" s="17">
         <f t="shared" si="0"/>
         <v>1.6890228566180887E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="45">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" s="18">
         <v>0.6</v>
       </c>
-      <c r="B13" s="45">
+      <c r="B13" s="18">
         <v>0.06</v>
       </c>
-      <c r="C13" s="45">
+      <c r="C13" s="18">
         <v>3.927</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="18">
         <v>1.0469999999999999</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="18">
         <v>1.4</v>
       </c>
-      <c r="F13" s="45">
-        <v>0</v>
-      </c>
-      <c r="G13" s="45">
-        <v>0</v>
-      </c>
-      <c r="H13" s="47">
+      <c r="F13" s="18">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <v>0</v>
+      </c>
+      <c r="H13" s="20">
         <v>-9.3124201521277395E-4</v>
       </c>
-      <c r="I13" s="47">
+      <c r="I13" s="20">
         <v>6.09082244336605E-2</v>
       </c>
-      <c r="J13" s="47">
+      <c r="J13" s="20">
         <v>-6.5952822566032396E-2</v>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="20">
         <v>0.391236692667007</v>
       </c>
-      <c r="L13" s="47">
+      <c r="L13" s="20">
         <v>-0.43392634391784701</v>
       </c>
-      <c r="M13" s="47">
+      <c r="M13" s="20">
         <v>-0.39902776479721103</v>
       </c>
-      <c r="N13" s="47">
+      <c r="N13" s="20">
         <v>-1.4374965089788497E-4</v>
       </c>
-      <c r="O13" s="47">
+      <c r="O13" s="20">
         <v>5.5564588604863886E-2</v>
       </c>
-      <c r="P13" s="47">
+      <c r="P13" s="20">
         <v>-5.5089972135175372E-2</v>
       </c>
-      <c r="Q13" s="47">
+      <c r="Q13" s="20">
         <v>0.29245613753683569</v>
       </c>
-      <c r="R13" s="47">
+      <c r="R13" s="20">
         <v>-0.36848237100366715</v>
       </c>
-      <c r="S13" s="47">
+      <c r="S13" s="20">
         <v>-0.37240942780979464</v>
       </c>
-      <c r="T13" s="44">
+      <c r="T13" s="17">
         <f t="shared" si="0"/>
         <v>7.8749236431488901E-4</v>
       </c>
-      <c r="U13" s="44">
+      <c r="U13" s="17">
         <f t="shared" si="0"/>
         <v>5.343635828796614E-3</v>
       </c>
-      <c r="V13" s="44">
+      <c r="V13" s="17">
         <f t="shared" si="0"/>
         <v>1.0862850430857024E-2</v>
       </c>
-      <c r="W13" s="44">
+      <c r="W13" s="17">
         <f t="shared" si="0"/>
         <v>9.878055513017131E-2</v>
       </c>
-      <c r="X13" s="44">
+      <c r="X13" s="17">
         <f t="shared" si="0"/>
         <v>6.544397291417986E-2</v>
       </c>
-      <c r="Y13" s="44">
+      <c r="Y13" s="17">
         <f t="shared" si="0"/>
         <v>2.6618336987416391E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="45">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14" s="18">
         <v>0.4</v>
       </c>
-      <c r="B14" s="45">
+      <c r="B14" s="18">
         <v>0.16</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="18">
         <v>3.927</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="18">
         <v>1.0469999999999999</v>
       </c>
-      <c r="E14" s="45">
-        <v>0</v>
-      </c>
-      <c r="F14" s="45">
-        <v>0</v>
-      </c>
-      <c r="G14" s="45">
-        <v>0</v>
-      </c>
-      <c r="H14" s="47">
+      <c r="E14" s="18">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
+        <v>0</v>
+      </c>
+      <c r="H14" s="20">
         <v>-2.4879071861505498E-4</v>
       </c>
-      <c r="I14" s="47">
+      <c r="I14" s="20">
         <v>5.3856808692216901E-2</v>
       </c>
-      <c r="J14" s="47">
+      <c r="J14" s="20">
         <v>-5.7678617537021602E-2</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="20">
         <v>0.14910565316677099</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="20">
         <v>-0.22375991940498399</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="20">
         <v>-0.20584329962730399</v>
       </c>
-      <c r="N14" s="47">
+      <c r="N14" s="20">
         <v>-1.2518597096840219E-18</v>
       </c>
-      <c r="O14" s="47">
+      <c r="O14" s="20">
         <v>6.5237777603792207E-2</v>
       </c>
-      <c r="P14" s="47">
+      <c r="P14" s="20">
         <v>-6.5236579456106641E-2</v>
       </c>
-      <c r="Q14" s="47">
+      <c r="Q14" s="20">
         <v>0.11248241702851622</v>
       </c>
-      <c r="R14" s="47">
+      <c r="R14" s="20">
         <v>-0.27142671653627698</v>
       </c>
-      <c r="S14" s="47">
+      <c r="S14" s="20">
         <v>-0.27143170161205693</v>
       </c>
-      <c r="T14" s="44">
+      <c r="T14" s="17">
         <f t="shared" si="0"/>
         <v>2.4879071861505373E-4</v>
       </c>
-      <c r="U14" s="44">
+      <c r="U14" s="17">
         <f t="shared" si="0"/>
         <v>1.1380968911575307E-2</v>
       </c>
-      <c r="V14" s="44">
+      <c r="V14" s="17">
         <f t="shared" si="0"/>
         <v>7.5579619190850392E-3</v>
       </c>
-      <c r="W14" s="44">
+      <c r="W14" s="17">
         <f t="shared" si="0"/>
         <v>3.6623236138254772E-2</v>
       </c>
-      <c r="X14" s="44">
+      <c r="X14" s="17">
         <f t="shared" si="0"/>
         <v>4.7666797131292987E-2</v>
       </c>
-      <c r="Y14" s="44">
+      <c r="Y14" s="17">
         <f t="shared" si="0"/>
         <v>6.5588401984752936E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="45">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="18">
         <v>0.8</v>
       </c>
-      <c r="B15" s="45">
+      <c r="B15" s="18">
         <v>0.06</v>
       </c>
-      <c r="C15" s="45">
+      <c r="C15" s="18">
         <v>4.7119999999999997</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="18">
         <v>0.78500000000000003</v>
       </c>
-      <c r="E15" s="45">
-        <v>0</v>
-      </c>
-      <c r="F15" s="45">
-        <v>0</v>
-      </c>
-      <c r="G15" s="45">
-        <v>0</v>
-      </c>
-      <c r="H15" s="47">
+      <c r="E15" s="18">
+        <v>0</v>
+      </c>
+      <c r="F15" s="18">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20">
         <v>-8.1355357542633999E-4</v>
       </c>
-      <c r="I15" s="47">
+      <c r="I15" s="20">
         <v>0.109302945435047</v>
       </c>
-      <c r="J15" s="47">
+      <c r="J15" s="20">
         <v>-9.5806457102298704E-4</v>
       </c>
-      <c r="K15" s="47">
+      <c r="K15" s="20">
         <v>0.61643946170806896</v>
       </c>
-      <c r="L15" s="47">
+      <c r="L15" s="20">
         <v>-9.5924139022827096E-3</v>
       </c>
-      <c r="M15" s="47">
+      <c r="M15" s="20">
         <v>-0.74946981668472301</v>
       </c>
-      <c r="N15" s="47">
+      <c r="N15" s="20">
         <v>1.7486654921155865E-22</v>
       </c>
-      <c r="O15" s="47">
+      <c r="O15" s="20">
         <v>8.8012694436971989E-2</v>
       </c>
-      <c r="P15" s="47">
+      <c r="P15" s="20">
         <v>-3.4235213466368205E-5</v>
       </c>
-      <c r="Q15" s="47">
+      <c r="Q15" s="20">
         <v>0.53476932149840273</v>
       </c>
-      <c r="R15" s="47">
+      <c r="R15" s="20">
         <v>-2.3144204426495354E-4</v>
       </c>
-      <c r="S15" s="47">
+      <c r="S15" s="20">
         <v>-0.59499666744506552</v>
       </c>
-      <c r="T15" s="44">
+      <c r="T15" s="17">
         <f t="shared" si="0"/>
         <v>8.1355357542633999E-4</v>
       </c>
-      <c r="U15" s="44">
+      <c r="U15" s="17">
         <f t="shared" si="0"/>
         <v>2.1290250998075008E-2</v>
       </c>
-      <c r="V15" s="44">
+      <c r="V15" s="17">
         <f t="shared" si="0"/>
         <v>9.2382935755661879E-4</v>
       </c>
-      <c r="W15" s="44">
+      <c r="W15" s="17">
         <f t="shared" si="0"/>
         <v>8.1670140209666231E-2</v>
       </c>
-      <c r="X15" s="44">
+      <c r="X15" s="17">
         <f t="shared" si="0"/>
         <v>9.3609718580177567E-3</v>
       </c>
-      <c r="Y15" s="44">
+      <c r="Y15" s="17">
         <f t="shared" si="0"/>
         <v>0.15447314923965749</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="45">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16" s="18">
         <v>0.5</v>
       </c>
-      <c r="B16" s="45">
+      <c r="B16" s="18">
         <v>0.1</v>
       </c>
-      <c r="C16" s="45">
+      <c r="C16" s="18">
         <v>4.7119999999999997</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="18">
         <v>1.0469999999999999</v>
       </c>
-      <c r="E16" s="45">
-        <v>0</v>
-      </c>
-      <c r="F16" s="45">
-        <v>0</v>
-      </c>
-      <c r="G16" s="45">
-        <v>0</v>
-      </c>
-      <c r="H16" s="47">
+      <c r="E16" s="18">
+        <v>0</v>
+      </c>
+      <c r="F16" s="18">
+        <v>0</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
+      <c r="H16" s="20">
         <v>-7.3147960938513301E-4</v>
       </c>
-      <c r="I16" s="47">
+      <c r="I16" s="20">
         <v>8.4560625255107894E-2</v>
       </c>
-      <c r="J16" s="47">
+      <c r="J16" s="20">
         <v>-6.7205965751782103E-4</v>
       </c>
-      <c r="K16" s="47">
+      <c r="K16" s="20">
         <v>0.244871556758881</v>
       </c>
-      <c r="L16" s="47">
+      <c r="L16" s="20">
         <v>-5.1593184471130397E-3</v>
       </c>
-      <c r="M16" s="47">
+      <c r="M16" s="20">
         <v>-0.443679749965668</v>
       </c>
-      <c r="N16" s="47">
+      <c r="N16" s="20">
         <v>2.556733407603453E-22</v>
       </c>
-      <c r="O16" s="47">
+      <c r="O16" s="20">
         <v>8.5505849026659878E-2</v>
       </c>
-      <c r="P16" s="47">
+      <c r="P16" s="20">
         <v>-3.3260099725126272E-5</v>
       </c>
-      <c r="Q16" s="47">
+      <c r="Q16" s="20">
         <v>0.19866354979713277</v>
       </c>
-      <c r="R16" s="47">
+      <c r="R16" s="20">
         <v>-1.78479054238076E-4</v>
       </c>
-      <c r="S16" s="47">
+      <c r="S16" s="20">
         <v>-0.4588381632113106</v>
       </c>
-      <c r="T16" s="44">
+      <c r="T16" s="17">
         <f t="shared" si="0"/>
         <v>7.3147960938513301E-4</v>
       </c>
-      <c r="U16" s="44">
+      <c r="U16" s="17">
         <f t="shared" si="0"/>
         <v>9.45223771551984E-4</v>
       </c>
-      <c r="V16" s="44">
+      <c r="V16" s="17">
         <f t="shared" si="0"/>
         <v>6.3879955779269474E-4</v>
       </c>
-      <c r="W16" s="44">
+      <c r="W16" s="17">
         <f t="shared" si="0"/>
         <v>4.6208006961748233E-2</v>
       </c>
-      <c r="X16" s="44">
+      <c r="X16" s="17">
         <f t="shared" si="0"/>
         <v>4.9808393928749634E-3</v>
       </c>
-      <c r="Y16" s="44">
+      <c r="Y16" s="17">
         <f t="shared" si="0"/>
         <v>1.5158413245642599E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="45">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17" s="18">
         <v>0.8</v>
       </c>
-      <c r="B17" s="45">
+      <c r="B17" s="18">
         <v>0.2</v>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="18">
         <v>4.7119999999999997</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="18">
         <v>1.571</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="18">
         <v>1.4</v>
       </c>
-      <c r="F17" s="45">
-        <v>0</v>
-      </c>
-      <c r="G17" s="45">
-        <v>0</v>
-      </c>
-      <c r="H17" s="47">
+      <c r="F17" s="18">
+        <v>0</v>
+      </c>
+      <c r="G17" s="18">
+        <v>0</v>
+      </c>
+      <c r="H17" s="20">
         <v>-1.0631438344717E-2</v>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="20">
         <v>0.203466981649399</v>
       </c>
-      <c r="J17" s="47">
+      <c r="J17" s="20">
         <v>-9.3788113445043599E-3</v>
       </c>
-      <c r="K17" s="47">
+      <c r="K17" s="20">
         <v>-0.43627014756202698</v>
       </c>
-      <c r="L17" s="47">
+      <c r="L17" s="20">
         <v>-5.16471415758133E-2</v>
       </c>
-      <c r="M17" s="47">
+      <c r="M17" s="20">
         <v>-0.57094836235046398</v>
       </c>
-      <c r="N17" s="47">
+      <c r="N17" s="20">
         <v>-7.8606351910923498E-3</v>
       </c>
-      <c r="O17" s="47">
+      <c r="O17" s="20">
         <v>0.20211787167080705</v>
       </c>
-      <c r="P17" s="47">
+      <c r="P17" s="20">
         <v>1.2172509209495667E-4</v>
       </c>
-      <c r="Q17" s="47">
+      <c r="Q17" s="20">
         <v>-0.5447156053886808</v>
       </c>
-      <c r="R17" s="47">
+      <c r="R17" s="20">
         <v>-2.0832083642786547E-2</v>
       </c>
-      <c r="S17" s="47">
+      <c r="S17" s="20">
         <v>-0.58553459361846427</v>
       </c>
-      <c r="T17" s="44">
+      <c r="T17" s="17">
         <f t="shared" si="0"/>
         <v>2.77080315362465E-3</v>
       </c>
-      <c r="U17" s="44">
+      <c r="U17" s="17">
         <f t="shared" si="0"/>
         <v>1.3491099785919447E-3</v>
       </c>
-      <c r="V17" s="44">
+      <c r="V17" s="17">
         <f t="shared" si="0"/>
         <v>9.5005364365993161E-3</v>
       </c>
-      <c r="W17" s="44">
+      <c r="W17" s="17">
         <f t="shared" si="0"/>
         <v>0.10844545782665382</v>
       </c>
-      <c r="X17" s="44">
+      <c r="X17" s="17">
         <f t="shared" si="0"/>
         <v>3.0815057933026753E-2</v>
       </c>
-      <c r="Y17" s="44">
+      <c r="Y17" s="17">
         <f t="shared" si="0"/>
         <v>1.4586231268000294E-2</v>
       </c>
@@ -8080,66 +8084,66 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D6F75F-00D5-499A-8B94-C01DFDD9DEC2}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" customWidth="1"/>
+    <col min="19" max="19" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7265625" customWidth="1"/>
+    <col min="23" max="23" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:26" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="39" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="31" t="s">
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="40" t="s">
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
       <c r="V1" s="16"/>
-      <c r="W1" s="49" t="s">
+      <c r="W1" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-    </row>
-    <row r="2" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+    </row>
+    <row r="2" spans="1:26" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
@@ -8219,1338 +8223,1296 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="47">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A3" s="20">
         <f>'Proximal Validation (single)'!A3</f>
         <v>0.7</v>
       </c>
-      <c r="B3" s="47">
+      <c r="B3" s="20">
         <f>'Proximal Validation (single)'!B3</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="20">
         <f>'Proximal Validation (single)'!C3</f>
         <v>1.571</v>
       </c>
-      <c r="D3" s="47">
+      <c r="D3" s="20">
         <f>'Proximal Validation (single)'!D3</f>
         <v>0.78500000000000003</v>
       </c>
-      <c r="E3" s="47">
+      <c r="E3" s="20">
         <f>'Proximal Validation (single)'!E3</f>
         <v>1.4</v>
       </c>
-      <c r="F3" s="47">
+      <c r="F3" s="20">
         <f>'Proximal Validation (single)'!F3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="47">
+      <c r="G3" s="20">
         <f>'Proximal Validation (single)'!G3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="47">
+      <c r="H3" s="20">
         <f>'Proximal Validation (single)'!H3</f>
         <v>6.98671909049153E-4</v>
       </c>
-      <c r="I3" s="47">
+      <c r="I3" s="20">
         <f>'Proximal Validation (single)'!I3</f>
         <v>-0.12202821671962701</v>
       </c>
-      <c r="J3" s="47">
+      <c r="J3" s="20">
         <f>'Proximal Validation (single)'!J3</f>
         <v>-3.2366467639803899E-3</v>
       </c>
-      <c r="K3" s="47">
+      <c r="K3" s="20">
         <f>'Proximal Validation (single)'!K3</f>
         <v>0.37189677357673601</v>
       </c>
-      <c r="L3" s="47">
+      <c r="L3" s="20">
         <f>'Proximal Validation (single)'!L3</f>
         <v>-5.3712725639343296E-3</v>
       </c>
-      <c r="M3" s="47">
+      <c r="M3" s="20">
         <f>'Proximal Validation (single)'!M3</f>
         <v>0.55187070369720503</v>
       </c>
-      <c r="N3" s="47">
+      <c r="N3" s="20">
         <v>0.66553370381714982</v>
       </c>
-      <c r="O3" s="47">
+      <c r="O3" s="20">
         <v>0.15738057594998922</v>
       </c>
-      <c r="P3" s="47">
+      <c r="P3" s="20">
         <v>1.6619899035034424</v>
       </c>
-      <c r="Q3" s="47">
+      <c r="Q3" s="20">
         <v>0.65217751542001379</v>
       </c>
-      <c r="R3" s="50">
+      <c r="R3" s="21">
         <v>4.6050657949341354E-6</v>
       </c>
-      <c r="S3" s="46">
+      <c r="S3" s="19">
         <f>ABS(N3-A3)</f>
         <v>3.4466296182850131E-2</v>
       </c>
-      <c r="T3" s="46">
+      <c r="T3" s="19">
         <f t="shared" ref="T3:V3" si="0">ABS(O3-B3)</f>
         <v>1.7380575949989208E-2</v>
       </c>
-      <c r="U3" s="46">
+      <c r="U3" s="19">
         <f t="shared" si="0"/>
         <v>9.0989903503442493E-2</v>
       </c>
-      <c r="V3" s="46">
+      <c r="V3" s="19">
         <f t="shared" si="0"/>
         <v>0.13282248457998624</v>
       </c>
-      <c r="W3" s="47">
+      <c r="W3" s="20">
         <f>AVERAGE(S3:S17)</f>
         <v>5.1930369997743545E-2</v>
       </c>
-      <c r="X3" s="47">
+      <c r="X3" s="20">
         <f t="shared" ref="X3:Z3" si="1">AVERAGE(T3:T17)</f>
         <v>9.4847545630054302E-3</v>
       </c>
-      <c r="Y3" s="47">
+      <c r="Y3" s="20">
         <f t="shared" si="1"/>
         <v>4.3917932975898182E-2</v>
       </c>
-      <c r="Z3" s="47">
+      <c r="Z3" s="20">
         <f t="shared" si="1"/>
         <v>0.10730696018085939</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="47">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A4" s="20">
         <f>'Proximal Validation (single)'!A4</f>
         <v>0.3</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="20">
         <f>'Proximal Validation (single)'!B4</f>
         <v>0.06</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="20">
         <f>'Proximal Validation (single)'!C4</f>
         <v>1.571</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="20">
         <f>'Proximal Validation (single)'!D4</f>
         <v>1.571</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="20">
         <f>'Proximal Validation (single)'!E4</f>
         <v>0</v>
       </c>
-      <c r="F4" s="47">
+      <c r="F4" s="20">
         <f>'Proximal Validation (single)'!F4</f>
         <v>0</v>
       </c>
-      <c r="G4" s="47">
+      <c r="G4" s="20">
         <f>'Proximal Validation (single)'!G4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="47">
+      <c r="H4" s="20">
         <f>'Proximal Validation (single)'!H4</f>
         <v>-3.4992315340787199E-4</v>
       </c>
-      <c r="I4" s="47">
+      <c r="I4" s="20">
         <f>'Proximal Validation (single)'!I4</f>
         <v>-4.4687353074550601E-2</v>
       </c>
-      <c r="J4" s="47">
+      <c r="J4" s="20">
         <f>'Proximal Validation (single)'!J4</f>
         <v>4.3301115510985303E-5</v>
       </c>
-      <c r="K4" s="47">
+      <c r="K4" s="20">
         <f>'Proximal Validation (single)'!K4</f>
         <v>-1.78173277527094E-3</v>
       </c>
-      <c r="L4" s="47">
+      <c r="L4" s="20">
         <f>'Proximal Validation (single)'!L4</f>
         <v>3.9914771914482099E-3</v>
       </c>
-      <c r="M4" s="47">
+      <c r="M4" s="20">
         <f>'Proximal Validation (single)'!M4</f>
         <v>0.286231309175491</v>
       </c>
-      <c r="N4" s="47">
+      <c r="N4" s="20">
         <v>0.28626471211728882</v>
       </c>
-      <c r="O4" s="47">
+      <c r="O4" s="20">
         <v>6.6212471584538996E-2</v>
       </c>
-      <c r="P4" s="47">
+      <c r="P4" s="20">
         <v>1.5571609397364092</v>
       </c>
-      <c r="Q4" s="47">
+      <c r="Q4" s="20">
         <v>1.544395658080858</v>
       </c>
-      <c r="R4" s="50">
+      <c r="R4" s="21">
         <v>4.5062338519249659E-7</v>
       </c>
-      <c r="S4" s="46">
+      <c r="S4" s="19">
         <f t="shared" ref="S4:S17" si="2">ABS(N4-A4)</f>
         <v>1.3735287882711167E-2</v>
       </c>
-      <c r="T4" s="46">
+      <c r="T4" s="19">
         <f t="shared" ref="T4:T17" si="3">ABS(O4-B4)</f>
         <v>6.2124715845389977E-3</v>
       </c>
-      <c r="U4" s="46">
+      <c r="U4" s="19">
         <f t="shared" ref="U4:U17" si="4">ABS(P4-C4)</f>
         <v>1.3839060263590719E-2</v>
       </c>
-      <c r="V4" s="46">
+      <c r="V4" s="19">
         <f t="shared" ref="V4:V17" si="5">ABS(Q4-D4)</f>
         <v>2.6604341919141961E-2</v>
       </c>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="47">
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A5" s="20">
         <f>'Proximal Validation (single)'!A5</f>
         <v>0.4</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="20">
         <f>'Proximal Validation (single)'!B5</f>
         <v>0.08</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="20">
         <f>'Proximal Validation (single)'!C5</f>
         <v>2.3559999999999999</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="20">
         <f>'Proximal Validation (single)'!D5</f>
         <v>0.52400000000000002</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="20">
         <f>'Proximal Validation (single)'!E5</f>
         <v>1.4</v>
       </c>
-      <c r="F5" s="47">
+      <c r="F5" s="20">
         <f>'Proximal Validation (single)'!F5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="20">
         <f>'Proximal Validation (single)'!G5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="47">
+      <c r="H5" s="20">
         <f>'Proximal Validation (single)'!H5</f>
         <v>-1.44779565744102E-4</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="20">
         <f>'Proximal Validation (single)'!I5</f>
         <v>-2.2709889337420502E-2</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="20">
         <f>'Proximal Validation (single)'!J5</f>
         <v>-2.47002802789211E-2</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="20">
         <f>'Proximal Validation (single)'!K5</f>
         <v>0.37153226137161299</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="20">
         <f>'Proximal Validation (single)'!L5</f>
         <v>-0.145699113607407</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="20">
         <f>'Proximal Validation (single)'!M5</f>
         <v>0.141014218330383</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="20">
         <v>0.42326187638852797</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="20">
         <v>7.7542999433408796E-2</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="20">
         <v>2.4533605830267806</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="20">
         <v>0.48311203702393002</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="21">
         <v>2.9113464117223297E-7</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="19">
         <f t="shared" si="2"/>
         <v>2.3261876388527947E-2</v>
       </c>
-      <c r="T5" s="46">
+      <c r="T5" s="19">
         <f t="shared" si="3"/>
         <v>2.4570005665912054E-3</v>
       </c>
-      <c r="U5" s="46">
+      <c r="U5" s="19">
         <f t="shared" si="4"/>
         <v>9.7360583026780745E-2</v>
       </c>
-      <c r="V5" s="46">
+      <c r="V5" s="19">
         <f t="shared" si="5"/>
         <v>4.0887962976070003E-2</v>
       </c>
-      <c r="W5" s="48"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="48"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="47">
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A6" s="20">
         <f>'Proximal Validation (single)'!A6</f>
         <v>0.4</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="20">
         <f>'Proximal Validation (single)'!B6</f>
         <v>0.2</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="20">
         <f>'Proximal Validation (single)'!C6</f>
         <v>2.3559999999999999</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="20">
         <f>'Proximal Validation (single)'!D6</f>
         <v>0.78500000000000003</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="20">
         <f>'Proximal Validation (single)'!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="20">
         <f>'Proximal Validation (single)'!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="20">
         <f>'Proximal Validation (single)'!G6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="47">
+      <c r="H6" s="20">
         <f>'Proximal Validation (single)'!H6</f>
         <v>9.3833426944911494E-5</v>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="20">
         <f>'Proximal Validation (single)'!I6</f>
         <v>-5.1531359553337097E-2</v>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="20">
         <f>'Proximal Validation (single)'!J6</f>
         <v>-5.3816821426153197E-2</v>
       </c>
-      <c r="K6" s="47">
+      <c r="K6" s="20">
         <f>'Proximal Validation (single)'!K6</f>
         <v>0.240476429462433</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="20">
         <f>'Proximal Validation (single)'!L6</f>
         <v>-0.18773703277111101</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="20">
         <f>'Proximal Validation (single)'!M6</f>
         <v>0.19507205486297599</v>
       </c>
-      <c r="N6" s="47">
+      <c r="N6" s="20">
         <v>0.36284935404269114</v>
       </c>
-      <c r="O6" s="47">
+      <c r="O6" s="20">
         <v>0.2</v>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="20">
         <v>2.3397474951297816</v>
       </c>
-      <c r="Q6" s="47">
+      <c r="Q6" s="20">
         <v>0.61916408640005771</v>
       </c>
-      <c r="R6" s="50">
+      <c r="R6" s="21">
         <v>2.7615904228789523E-5</v>
       </c>
-      <c r="S6" s="46">
+      <c r="S6" s="19">
         <f t="shared" si="2"/>
         <v>3.7150645957308881E-2</v>
       </c>
-      <c r="T6" s="46">
+      <c r="T6" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U6" s="46">
+      <c r="U6" s="19">
         <f t="shared" si="4"/>
         <v>1.6252504870218232E-2</v>
       </c>
-      <c r="V6" s="46">
+      <c r="V6" s="19">
         <f t="shared" si="5"/>
         <v>0.16583591359994232</v>
       </c>
-      <c r="W6" s="48"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="48"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="47">
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A7" s="20">
         <f>'Proximal Validation (single)'!A7</f>
         <v>0.8</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="20">
         <f>'Proximal Validation (single)'!B7</f>
         <v>0.1</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="20">
         <f>'Proximal Validation (single)'!C7</f>
         <v>2.3559999999999999</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="20">
         <f>'Proximal Validation (single)'!D7</f>
         <v>1.0469999999999999</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="20">
         <f>'Proximal Validation (single)'!E7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="20">
         <f>'Proximal Validation (single)'!F7</f>
         <v>0</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="20">
         <f>'Proximal Validation (single)'!G7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="47">
+      <c r="H7" s="20">
         <f>'Proximal Validation (single)'!H7</f>
         <v>-4.4502015225589302E-4</v>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="20">
         <f>'Proximal Validation (single)'!I7</f>
         <v>-0.103923052549362</v>
       </c>
-      <c r="J7" s="47">
+      <c r="J7" s="20">
         <f>'Proximal Validation (single)'!J7</f>
         <v>-0.113764069974422</v>
       </c>
-      <c r="K7" s="47">
+      <c r="K7" s="20">
         <f>'Proximal Validation (single)'!K7</f>
         <v>0.34864503145217901</v>
       </c>
-      <c r="L7" s="47">
+      <c r="L7" s="20">
         <f>'Proximal Validation (single)'!L7</f>
         <v>-0.591894090175629</v>
       </c>
-      <c r="M7" s="47">
+      <c r="M7" s="20">
         <f>'Proximal Validation (single)'!M7</f>
         <v>0.56364732980728105</v>
       </c>
-      <c r="N7" s="47">
+      <c r="N7" s="20">
         <v>0.88859017790124883</v>
       </c>
-      <c r="O7" s="47">
+      <c r="O7" s="20">
         <v>0.10647146489245243</v>
       </c>
-      <c r="P7" s="47">
+      <c r="P7" s="20">
         <v>2.381345743621313</v>
       </c>
-      <c r="Q7" s="47">
+      <c r="Q7" s="20">
         <v>0.94641192898971005</v>
       </c>
-      <c r="R7" s="50">
+      <c r="R7" s="21">
         <v>1.0055766771265992E-5</v>
       </c>
-      <c r="S7" s="46">
+      <c r="S7" s="19">
         <f t="shared" si="2"/>
         <v>8.859017790124879E-2</v>
       </c>
-      <c r="T7" s="46">
+      <c r="T7" s="19">
         <f t="shared" si="3"/>
         <v>6.4714648924524276E-3</v>
       </c>
-      <c r="U7" s="46">
+      <c r="U7" s="19">
         <f t="shared" si="4"/>
         <v>2.5345743621313144E-2</v>
       </c>
-      <c r="V7" s="46">
+      <c r="V7" s="19">
         <f t="shared" si="5"/>
         <v>0.10058807101028988</v>
       </c>
-      <c r="W7" s="48"/>
-      <c r="X7" s="48"/>
-      <c r="Y7" s="48"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="47">
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A8" s="20">
         <f>'Proximal Validation (single)'!A8</f>
         <v>0.7</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="20">
         <f>'Proximal Validation (single)'!B8</f>
         <v>0.18</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="20">
         <f>'Proximal Validation (single)'!C8</f>
         <v>2.3559999999999999</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="20">
         <f>'Proximal Validation (single)'!D8</f>
         <v>1.0469999999999999</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="20">
         <f>'Proximal Validation (single)'!E8</f>
         <v>1.4</v>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="20">
         <f>'Proximal Validation (single)'!F8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="20">
         <f>'Proximal Validation (single)'!G8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="47">
+      <c r="H8" s="20">
         <f>'Proximal Validation (single)'!H8</f>
         <v>1.9051980000000001E-3</v>
       </c>
-      <c r="I8" s="47">
+      <c r="I8" s="20">
         <f>'Proximal Validation (single)'!I8</f>
         <v>-0.11076053199999999</v>
       </c>
-      <c r="J8" s="47">
+      <c r="J8" s="20">
         <f>'Proximal Validation (single)'!J8</f>
         <v>-0.130388632</v>
       </c>
-      <c r="K8" s="47">
+      <c r="K8" s="20">
         <f>'Proximal Validation (single)'!K8</f>
         <v>0.142369151</v>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="20">
         <f>'Proximal Validation (single)'!L8</f>
         <v>-0.47970119100000003</v>
       </c>
-      <c r="M8" s="47">
+      <c r="M8" s="20">
         <f>'Proximal Validation (single)'!M8</f>
         <v>0.43018263600000001</v>
       </c>
-      <c r="N8" s="47">
+      <c r="N8" s="20">
         <v>0.66071419584820568</v>
       </c>
-      <c r="O8" s="47">
+      <c r="O8" s="20">
         <v>0.2</v>
       </c>
-      <c r="P8" s="47">
+      <c r="P8" s="20">
         <v>2.4780464974154248</v>
       </c>
-      <c r="Q8" s="47">
+      <c r="Q8" s="20">
         <v>0.85288013948389818</v>
       </c>
-      <c r="R8" s="50">
+      <c r="R8" s="21">
         <v>4.0466123998574682E-5</v>
       </c>
-      <c r="S8" s="46">
+      <c r="S8" s="19">
         <f t="shared" si="2"/>
         <v>3.9285804151794279E-2</v>
       </c>
-      <c r="T8" s="46">
+      <c r="T8" s="19">
         <f t="shared" si="3"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="U8" s="46">
+      <c r="U8" s="19">
         <f t="shared" si="4"/>
         <v>0.12204649741542495</v>
       </c>
-      <c r="V8" s="46">
+      <c r="V8" s="19">
         <f t="shared" si="5"/>
         <v>0.19411986051610175</v>
       </c>
-      <c r="W8" s="48"/>
-      <c r="X8" s="48"/>
-      <c r="Y8" s="48"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="47">
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A9" s="20">
         <f>'Proximal Validation (single)'!A9</f>
         <v>0.7</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="20">
         <f>'Proximal Validation (single)'!B9</f>
         <v>0.08</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="20">
         <f>'Proximal Validation (single)'!C9</f>
         <v>3.1419999999999999</v>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="20">
         <f>'Proximal Validation (single)'!D9</f>
         <v>1.571</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="20">
         <f>'Proximal Validation (single)'!E9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="20">
         <f>'Proximal Validation (single)'!F9</f>
         <v>0</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="20">
         <f>'Proximal Validation (single)'!G9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="47">
+      <c r="H9" s="20">
         <f>'Proximal Validation (single)'!H9</f>
         <v>-1.2491350062191499E-3</v>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="20">
         <f>'Proximal Validation (single)'!I9</f>
         <v>1.1835042387247101E-3</v>
       </c>
-      <c r="J9" s="47">
+      <c r="J9" s="20">
         <f>'Proximal Validation (single)'!J9</f>
         <v>-0.12853877246379899</v>
       </c>
-      <c r="K9" s="47">
+      <c r="K9" s="20">
         <f>'Proximal Validation (single)'!K9</f>
         <v>-4.8892773687839501E-2</v>
       </c>
-      <c r="L9" s="47">
+      <c r="L9" s="20">
         <f>'Proximal Validation (single)'!L9</f>
         <v>-0.72314238548278797</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="20">
         <f>'Proximal Validation (single)'!M9</f>
         <v>5.8930516242981E-3</v>
       </c>
-      <c r="N9" s="47">
+      <c r="N9" s="20">
         <v>0.72481831057967783</v>
       </c>
-      <c r="O9" s="47">
+      <c r="O9" s="20">
         <v>8.7670496689563268E-2</v>
       </c>
-      <c r="P9" s="47">
+      <c r="P9" s="20">
         <v>3.1339750940689584</v>
       </c>
-      <c r="Q9" s="47">
+      <c r="Q9" s="20">
         <v>1.493000585486729</v>
       </c>
-      <c r="R9" s="50">
+      <c r="R9" s="21">
         <v>6.3849567508938255E-6</v>
       </c>
-      <c r="S9" s="46">
+      <c r="S9" s="19">
         <f t="shared" si="2"/>
         <v>2.4818310579677871E-2</v>
       </c>
-      <c r="T9" s="46">
+      <c r="T9" s="19">
         <f t="shared" si="3"/>
         <v>7.6704966895632665E-3</v>
       </c>
-      <c r="U9" s="46">
+      <c r="U9" s="19">
         <f t="shared" si="4"/>
         <v>8.0249059310415483E-3</v>
       </c>
-      <c r="V9" s="46">
+      <c r="V9" s="19">
         <f t="shared" si="5"/>
         <v>7.799941451327097E-2</v>
       </c>
-      <c r="W9" s="48"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="47">
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A10" s="20">
         <f>'Proximal Validation (single)'!A10</f>
         <v>0.4</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="20">
         <f>'Proximal Validation (single)'!B10</f>
         <v>0.16</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="20">
         <f>'Proximal Validation (single)'!C10</f>
         <v>3.1419999999999999</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="20">
         <f>'Proximal Validation (single)'!D10</f>
         <v>1.571</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="20">
         <f>'Proximal Validation (single)'!E10</f>
         <v>1.4</v>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="20">
         <f>'Proximal Validation (single)'!F10</f>
         <v>0</v>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="20">
         <f>'Proximal Validation (single)'!G10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="47">
+      <c r="H10" s="20">
         <f>'Proximal Validation (single)'!H10</f>
         <v>1.3951195869594799E-3</v>
       </c>
-      <c r="I10" s="47">
+      <c r="I10" s="20">
         <f>'Proximal Validation (single)'!I10</f>
         <v>3.4124546218663502E-3</v>
       </c>
-      <c r="J10" s="47">
+      <c r="J10" s="20">
         <f>'Proximal Validation (single)'!J10</f>
         <v>-0.112820729613304</v>
       </c>
-      <c r="K10" s="47">
+      <c r="K10" s="20">
         <f>'Proximal Validation (single)'!K10</f>
         <v>-4.2202740907669102E-2</v>
       </c>
-      <c r="L10" s="47">
+      <c r="L10" s="20">
         <f>'Proximal Validation (single)'!L10</f>
         <v>-0.417444437742233</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="20">
         <f>'Proximal Validation (single)'!M10</f>
         <v>-3.7499666213989301E-3</v>
       </c>
-      <c r="N10" s="47">
+      <c r="N10" s="20">
         <v>0.41959701845866498</v>
       </c>
-      <c r="O10" s="47">
+      <c r="O10" s="20">
         <v>0.18011359072516081</v>
       </c>
-      <c r="P10" s="47">
+      <c r="P10" s="20">
         <v>3.1568856741697093</v>
       </c>
-      <c r="Q10" s="47">
+      <c r="Q10" s="20">
         <v>1.4071034843347032</v>
       </c>
-      <c r="R10" s="50">
+      <c r="R10" s="21">
         <v>6.6092918515787231E-6</v>
       </c>
-      <c r="S10" s="46">
+      <c r="S10" s="19">
         <f t="shared" si="2"/>
         <v>1.9597018458664961E-2</v>
       </c>
-      <c r="T10" s="46">
+      <c r="T10" s="19">
         <f t="shared" si="3"/>
         <v>2.0113590725160807E-2</v>
       </c>
-      <c r="U10" s="46">
+      <c r="U10" s="19">
         <f t="shared" si="4"/>
         <v>1.4885674169709429E-2</v>
       </c>
-      <c r="V10" s="46">
+      <c r="V10" s="19">
         <f t="shared" si="5"/>
         <v>0.16389651566529673</v>
       </c>
-      <c r="W10" s="48"/>
-      <c r="X10" s="48"/>
-      <c r="Y10" s="48"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="47">
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" s="20">
         <f>'Proximal Validation (single)'!A11</f>
         <v>0.7</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="20">
         <f>'Proximal Validation (single)'!B11</f>
         <v>0.18</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="20">
         <f>'Proximal Validation (single)'!C11</f>
         <v>3.927</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="20">
         <f>'Proximal Validation (single)'!D11</f>
         <v>0.52400000000000002</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="20">
         <f>'Proximal Validation (single)'!E11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="20">
         <f>'Proximal Validation (single)'!F11</f>
         <v>0</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="20">
         <f>'Proximal Validation (single)'!G11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="47">
+      <c r="H11" s="20">
         <f>'Proximal Validation (single)'!H11</f>
         <v>-9.7516691312193898E-5</v>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="20">
         <f>'Proximal Validation (single)'!I11</f>
         <v>6.3756838440895094E-2</v>
       </c>
-      <c r="J11" s="47">
+      <c r="J11" s="20">
         <f>'Proximal Validation (single)'!J11</f>
         <v>-6.7828088998794597E-2</v>
       </c>
-      <c r="K11" s="47">
+      <c r="K11" s="20">
         <f>'Proximal Validation (single)'!K11</f>
         <v>0.525340616703033</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="20">
         <f>'Proximal Validation (single)'!L11</f>
         <v>-0.27887076139450101</v>
       </c>
-      <c r="M11" s="47">
+      <c r="M11" s="20">
         <f>'Proximal Validation (single)'!M11</f>
         <v>-0.25877004861831698</v>
       </c>
-      <c r="N11" s="47">
+      <c r="N11" s="20">
         <v>0.64900396283548345</v>
       </c>
-      <c r="O11" s="47">
+      <c r="O11" s="20">
         <v>0.2</v>
       </c>
-      <c r="P11" s="47">
+      <c r="P11" s="20">
         <v>3.889972408616047</v>
       </c>
-      <c r="Q11" s="47">
+      <c r="Q11" s="20">
         <v>0.36446009848349892</v>
       </c>
-      <c r="R11" s="50">
+      <c r="R11" s="21">
         <v>1.1527251465622725E-5</v>
       </c>
-      <c r="S11" s="46">
+      <c r="S11" s="19">
         <f t="shared" si="2"/>
         <v>5.0996037164516506E-2</v>
       </c>
-      <c r="T11" s="46">
+      <c r="T11" s="19">
         <f t="shared" si="3"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="U11" s="46">
+      <c r="U11" s="19">
         <f t="shared" si="4"/>
         <v>3.7027591383953062E-2</v>
       </c>
-      <c r="V11" s="46">
+      <c r="V11" s="19">
         <f t="shared" si="5"/>
         <v>0.1595399015165011</v>
       </c>
-      <c r="W11" s="48"/>
-      <c r="X11" s="48"/>
-      <c r="Y11" s="48"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="47">
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A12" s="20">
         <f>'Proximal Validation (single)'!A12</f>
         <v>0.3</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="20">
         <f>'Proximal Validation (single)'!B12</f>
         <v>0.1</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="20">
         <f>'Proximal Validation (single)'!C12</f>
         <v>3.927</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="20">
         <f>'Proximal Validation (single)'!D12</f>
         <v>0.78500000000000003</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="20">
         <f>'Proximal Validation (single)'!E12</f>
         <v>1.4</v>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="20">
         <f>'Proximal Validation (single)'!F12</f>
         <v>0</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="20">
         <f>'Proximal Validation (single)'!G12</f>
         <v>0</v>
       </c>
-      <c r="H12" s="47">
+      <c r="H12" s="20">
         <f>'Proximal Validation (single)'!H12</f>
         <v>-4.7630793415010003E-4</v>
       </c>
-      <c r="I12" s="47">
+      <c r="I12" s="20">
         <f>'Proximal Validation (single)'!I12</f>
         <v>2.59361006319523E-2</v>
       </c>
-      <c r="J12" s="47">
+      <c r="J12" s="20">
         <f>'Proximal Validation (single)'!J12</f>
         <v>-2.8502099215984299E-2</v>
       </c>
-      <c r="K12" s="47">
+      <c r="K12" s="20">
         <f>'Proximal Validation (single)'!K12</f>
         <v>0.25695684552192699</v>
       </c>
-      <c r="L12" s="47">
+      <c r="L12" s="20">
         <f>'Proximal Validation (single)'!L12</f>
         <v>-0.14679136872291601</v>
       </c>
-      <c r="M12" s="47">
+      <c r="M12" s="20">
         <f>'Proximal Validation (single)'!M12</f>
         <v>-0.135155409574509</v>
       </c>
-      <c r="N12" s="47">
+      <c r="N12" s="20">
         <v>0.32533342939907461</v>
       </c>
-      <c r="O12" s="47">
+      <c r="O12" s="20">
         <v>0.10415395306424298</v>
       </c>
-      <c r="P12" s="47">
+      <c r="P12" s="20">
         <v>3.8691866009876006</v>
       </c>
-      <c r="Q12" s="47">
+      <c r="Q12" s="20">
         <v>0.66372259924361143</v>
       </c>
-      <c r="R12" s="50">
+      <c r="R12" s="21">
         <v>1.2180167569624732E-7</v>
       </c>
-      <c r="S12" s="46">
+      <c r="S12" s="19">
         <f t="shared" si="2"/>
         <v>2.5333429399074625E-2</v>
       </c>
-      <c r="T12" s="46">
+      <c r="T12" s="19">
         <f t="shared" si="3"/>
         <v>4.1539530642429739E-3</v>
       </c>
-      <c r="U12" s="46">
+      <c r="U12" s="19">
         <f t="shared" si="4"/>
         <v>5.7813399012399458E-2</v>
       </c>
-      <c r="V12" s="46">
+      <c r="V12" s="19">
         <f t="shared" si="5"/>
         <v>0.1212774007563886</v>
       </c>
-      <c r="W12" s="48"/>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="47">
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" s="20">
         <f>'Proximal Validation (single)'!A13</f>
         <v>0.6</v>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="20">
         <f>'Proximal Validation (single)'!B13</f>
         <v>0.06</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="20">
         <f>'Proximal Validation (single)'!C13</f>
         <v>3.927</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="20">
         <f>'Proximal Validation (single)'!D13</f>
         <v>1.0469999999999999</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="20">
         <f>'Proximal Validation (single)'!E13</f>
         <v>1.4</v>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="20">
         <f>'Proximal Validation (single)'!F13</f>
         <v>0</v>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="20">
         <f>'Proximal Validation (single)'!G13</f>
         <v>0</v>
       </c>
-      <c r="H13" s="47">
+      <c r="H13" s="20">
         <f>'Proximal Validation (single)'!H13</f>
         <v>-9.3124201521277395E-4</v>
       </c>
-      <c r="I13" s="47">
+      <c r="I13" s="20">
         <f>'Proximal Validation (single)'!I13</f>
         <v>6.09082244336605E-2</v>
       </c>
-      <c r="J13" s="47">
+      <c r="J13" s="20">
         <f>'Proximal Validation (single)'!J13</f>
         <v>-6.5952822566032396E-2</v>
       </c>
-      <c r="K13" s="47">
+      <c r="K13" s="20">
         <f>'Proximal Validation (single)'!K13</f>
         <v>0.391236692667007</v>
       </c>
-      <c r="L13" s="47">
+      <c r="L13" s="20">
         <f>'Proximal Validation (single)'!L13</f>
         <v>-0.43392634391784701</v>
       </c>
-      <c r="M13" s="47">
+      <c r="M13" s="20">
         <f>'Proximal Validation (single)'!M13</f>
         <v>-0.39902776479721103</v>
       </c>
-      <c r="N13" s="47">
+      <c r="N13" s="20">
         <v>0.70740000000000003</v>
       </c>
-      <c r="O13" s="47">
+      <c r="O13" s="20">
         <v>6.3500000000000001E-2</v>
       </c>
-      <c r="P13" s="47">
+      <c r="P13" s="20">
         <v>3.8795999999999999</v>
       </c>
-      <c r="Q13" s="47">
+      <c r="Q13" s="20">
         <v>0.96079999999999999</v>
       </c>
-      <c r="R13" s="50">
+      <c r="R13" s="21">
         <v>8.3501330000000002E-7</v>
       </c>
-      <c r="S13" s="46">
+      <c r="S13" s="19">
         <f t="shared" si="2"/>
         <v>0.10740000000000005</v>
       </c>
-      <c r="T13" s="46">
+      <c r="T13" s="19">
         <f t="shared" si="3"/>
         <v>3.5000000000000031E-3</v>
       </c>
-      <c r="U13" s="46">
+      <c r="U13" s="19">
         <f t="shared" si="4"/>
         <v>4.7400000000000109E-2</v>
       </c>
-      <c r="V13" s="46">
+      <c r="V13" s="19">
         <f t="shared" si="5"/>
         <v>8.6199999999999943E-2</v>
       </c>
-      <c r="W13" s="48"/>
-      <c r="X13" s="48"/>
-      <c r="Y13" s="48"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="47">
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A14" s="20">
         <f>'Proximal Validation (single)'!A14</f>
         <v>0.4</v>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="20">
         <f>'Proximal Validation (single)'!B14</f>
         <v>0.16</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="20">
         <f>'Proximal Validation (single)'!C14</f>
         <v>3.927</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="20">
         <f>'Proximal Validation (single)'!D14</f>
         <v>1.0469999999999999</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="20">
         <f>'Proximal Validation (single)'!E14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="20">
         <f>'Proximal Validation (single)'!F14</f>
         <v>0</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="20">
         <f>'Proximal Validation (single)'!G14</f>
         <v>0</v>
       </c>
-      <c r="H14" s="47">
+      <c r="H14" s="20">
         <f>'Proximal Validation (single)'!H14</f>
         <v>-2.4879071861505498E-4</v>
       </c>
-      <c r="I14" s="47">
+      <c r="I14" s="20">
         <f>'Proximal Validation (single)'!I14</f>
         <v>5.3856808692216901E-2</v>
       </c>
-      <c r="J14" s="47">
+      <c r="J14" s="20">
         <f>'Proximal Validation (single)'!J14</f>
         <v>-5.7678617537021602E-2</v>
       </c>
-      <c r="K14" s="47">
+      <c r="K14" s="20">
         <f>'Proximal Validation (single)'!K14</f>
         <v>0.14910565316677099</v>
       </c>
-      <c r="L14" s="47">
+      <c r="L14" s="20">
         <f>'Proximal Validation (single)'!L14</f>
         <v>-0.22375991940498399</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="20">
         <f>'Proximal Validation (single)'!M14</f>
         <v>-0.20584329962730399</v>
       </c>
-      <c r="N14" s="47">
+      <c r="N14" s="20">
         <v>0.33863321445461042</v>
       </c>
-      <c r="O14" s="47">
+      <c r="O14" s="20">
         <v>0.18659092812231431</v>
       </c>
-      <c r="P14" s="47">
+      <c r="P14" s="20">
         <v>3.8857787896733096</v>
       </c>
-      <c r="Q14" s="47">
+      <c r="Q14" s="20">
         <v>0.86719610277952164</v>
       </c>
-      <c r="R14" s="50">
+      <c r="R14" s="21">
         <v>3.8387727145335275E-7</v>
       </c>
-      <c r="S14" s="46">
+      <c r="S14" s="19">
         <f t="shared" si="2"/>
         <v>6.1366785545389602E-2</v>
       </c>
-      <c r="T14" s="46">
+      <c r="T14" s="19">
         <f t="shared" si="3"/>
         <v>2.6590928122314311E-2</v>
       </c>
-      <c r="U14" s="46">
+      <c r="U14" s="19">
         <f t="shared" si="4"/>
         <v>4.1221210326690461E-2</v>
       </c>
-      <c r="V14" s="46">
+      <c r="V14" s="19">
         <f t="shared" si="5"/>
         <v>0.17980389722047829</v>
       </c>
-      <c r="W14" s="48"/>
-      <c r="X14" s="48"/>
-      <c r="Y14" s="48"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="47">
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A15" s="20">
         <f>'Proximal Validation (single)'!A15</f>
         <v>0.8</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="20">
         <f>'Proximal Validation (single)'!B15</f>
         <v>0.06</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="20">
         <f>'Proximal Validation (single)'!C15</f>
         <v>4.7119999999999997</v>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="20">
         <f>'Proximal Validation (single)'!D15</f>
         <v>0.78500000000000003</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="20">
         <f>'Proximal Validation (single)'!E15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="20">
         <f>'Proximal Validation (single)'!F15</f>
         <v>0</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="20">
         <f>'Proximal Validation (single)'!G15</f>
         <v>0</v>
       </c>
-      <c r="H15" s="47">
+      <c r="H15" s="20">
         <f>'Proximal Validation (single)'!H15</f>
         <v>-8.1355357542633999E-4</v>
       </c>
-      <c r="I15" s="47">
+      <c r="I15" s="20">
         <f>'Proximal Validation (single)'!I15</f>
         <v>0.109302945435047</v>
       </c>
-      <c r="J15" s="47">
+      <c r="J15" s="20">
         <f>'Proximal Validation (single)'!J15</f>
         <v>-9.5806457102298704E-4</v>
       </c>
-      <c r="K15" s="47">
+      <c r="K15" s="20">
         <f>'Proximal Validation (single)'!K15</f>
         <v>0.61643946170806896</v>
       </c>
-      <c r="L15" s="47">
+      <c r="L15" s="20">
         <f>'Proximal Validation (single)'!L15</f>
         <v>-9.5924139022827096E-3</v>
       </c>
-      <c r="M15" s="47">
+      <c r="M15" s="20">
         <f>'Proximal Validation (single)'!M15</f>
         <v>-0.74946981668472301</v>
       </c>
-      <c r="N15" s="47">
+      <c r="N15" s="20">
         <v>0.97046185508299676</v>
       </c>
-      <c r="O15" s="47">
+      <c r="O15" s="20">
         <v>5.7996012672311505E-2</v>
       </c>
-      <c r="P15" s="47">
+      <c r="P15" s="20">
         <v>4.6996747360299542</v>
       </c>
-      <c r="Q15" s="47">
+      <c r="Q15" s="20">
         <v>0.819476655689795</v>
       </c>
-      <c r="R15" s="50">
+      <c r="R15" s="21">
         <v>8.5218025262179853E-7</v>
       </c>
-      <c r="S15" s="46">
+      <c r="S15" s="19">
         <f t="shared" si="2"/>
         <v>0.17046185508299672</v>
       </c>
-      <c r="T15" s="46">
+      <c r="T15" s="19">
         <f t="shared" si="3"/>
         <v>2.0039873276884931E-3</v>
       </c>
-      <c r="U15" s="46">
+      <c r="U15" s="19">
         <f t="shared" si="4"/>
         <v>1.2325263970045519E-2</v>
       </c>
-      <c r="V15" s="46">
+      <c r="V15" s="19">
         <f t="shared" si="5"/>
         <v>3.4476655689794966E-2</v>
       </c>
-      <c r="W15" s="48"/>
-      <c r="X15" s="48"/>
-      <c r="Y15" s="48"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="47">
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16" s="20">
         <f>'Proximal Validation (single)'!A16</f>
         <v>0.5</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="20">
         <f>'Proximal Validation (single)'!B16</f>
         <v>0.1</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="20">
         <f>'Proximal Validation (single)'!C16</f>
         <v>4.7119999999999997</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="20">
         <f>'Proximal Validation (single)'!D16</f>
         <v>1.0469999999999999</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="20">
         <f>'Proximal Validation (single)'!E16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="20">
         <f>'Proximal Validation (single)'!F16</f>
         <v>0</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="20">
         <f>'Proximal Validation (single)'!G16</f>
         <v>0</v>
       </c>
-      <c r="H16" s="47">
+      <c r="H16" s="20">
         <f>'Proximal Validation (single)'!H16</f>
         <v>-7.3147960938513301E-4</v>
       </c>
-      <c r="I16" s="47">
+      <c r="I16" s="20">
         <f>'Proximal Validation (single)'!I16</f>
         <v>8.4560625255107894E-2</v>
       </c>
-      <c r="J16" s="47">
+      <c r="J16" s="20">
         <f>'Proximal Validation (single)'!J16</f>
         <v>-6.7205965751782103E-4</v>
       </c>
-      <c r="K16" s="47">
+      <c r="K16" s="20">
         <f>'Proximal Validation (single)'!K16</f>
         <v>0.244871556758881</v>
       </c>
-      <c r="L16" s="47">
+      <c r="L16" s="20">
         <f>'Proximal Validation (single)'!L16</f>
         <v>-5.1593184471130397E-3</v>
       </c>
-      <c r="M16" s="47">
+      <c r="M16" s="20">
         <f>'Proximal Validation (single)'!M16</f>
         <v>-0.443679749965668</v>
       </c>
-      <c r="N16" s="47">
+      <c r="N16" s="20">
         <v>0.50679452122129187</v>
       </c>
-      <c r="O16" s="47">
+      <c r="O16" s="20">
         <v>0.10571684952253972</v>
       </c>
-      <c r="P16" s="47">
+      <c r="P16" s="20">
         <v>4.7008900249719519</v>
       </c>
-      <c r="Q16" s="47">
+      <c r="Q16" s="20">
         <v>0.94371344856950157</v>
       </c>
-      <c r="R16" s="50">
+      <c r="R16" s="21">
         <v>6.2853213225997197E-7</v>
       </c>
-      <c r="S16" s="46">
+      <c r="S16" s="19">
         <f t="shared" si="2"/>
         <v>6.7945212212918715E-3</v>
       </c>
-      <c r="T16" s="46">
+      <c r="T16" s="19">
         <f t="shared" si="3"/>
         <v>5.7168495225397159E-3</v>
       </c>
-      <c r="U16" s="46">
+      <c r="U16" s="19">
         <f t="shared" si="4"/>
         <v>1.1109975028047891E-2</v>
       </c>
-      <c r="V16" s="46">
+      <c r="V16" s="19">
         <f t="shared" si="5"/>
         <v>0.10328655143049836</v>
       </c>
-      <c r="W16" s="48"/>
-      <c r="X16" s="48"/>
-      <c r="Y16" s="48"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="47">
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A17" s="20">
         <f>'Proximal Validation (single)'!A17</f>
         <v>0.8</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="20">
         <f>'Proximal Validation (single)'!B17</f>
         <v>0.2</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="20">
         <f>'Proximal Validation (single)'!C17</f>
         <v>4.7119999999999997</v>
       </c>
-      <c r="D17" s="47">
+      <c r="D17" s="20">
         <f>'Proximal Validation (single)'!D17</f>
         <v>1.571</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="20">
         <f>'Proximal Validation (single)'!E17</f>
         <v>1.4</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="20">
         <f>'Proximal Validation (single)'!F17</f>
         <v>0</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="20">
         <f>'Proximal Validation (single)'!G17</f>
         <v>0</v>
       </c>
-      <c r="H17" s="47">
+      <c r="H17" s="20">
         <f>'Proximal Validation (single)'!H17</f>
         <v>-1.0631438344717E-2</v>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="20">
         <f>'Proximal Validation (single)'!I17</f>
         <v>0.203466981649399</v>
       </c>
-      <c r="J17" s="47">
+      <c r="J17" s="20">
         <f>'Proximal Validation (single)'!J17</f>
         <v>-9.3788113445043599E-3</v>
       </c>
-      <c r="K17" s="47">
+      <c r="K17" s="20">
         <f>'Proximal Validation (single)'!K17</f>
         <v>-0.43627014756202698</v>
       </c>
-      <c r="L17" s="47">
+      <c r="L17" s="20">
         <f>'Proximal Validation (single)'!L17</f>
         <v>-5.16471415758133E-2</v>
       </c>
-      <c r="M17" s="47">
+      <c r="M17" s="20">
         <f>'Proximal Validation (single)'!M17</f>
         <v>-0.57094836235046398</v>
       </c>
-      <c r="N17" s="47">
+      <c r="N17" s="20">
         <v>0.72430249594990037</v>
       </c>
-      <c r="O17" s="47">
+      <c r="O17" s="20">
         <v>0.2</v>
       </c>
-      <c r="P17" s="47">
+      <c r="P17" s="20">
         <v>4.6488733178841848</v>
       </c>
-      <c r="Q17" s="47">
+      <c r="Q17" s="20">
         <v>1.54873456868087</v>
       </c>
-      <c r="R17" s="50">
+      <c r="R17" s="21">
         <v>2.4335240627389838E-4</v>
       </c>
-      <c r="S17" s="46">
+      <c r="S17" s="19">
         <f t="shared" si="2"/>
         <v>7.5697504050099673E-2</v>
       </c>
-      <c r="T17" s="46">
+      <c r="T17" s="19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U17" s="46">
+      <c r="U17" s="19">
         <f t="shared" si="4"/>
         <v>6.3126682115814958E-2</v>
       </c>
-      <c r="V17" s="46">
+      <c r="V17" s="19">
         <f t="shared" si="5"/>
         <v>2.2265431319129947E-2</v>
       </c>
-      <c r="W17" s="48"/>
-      <c r="X17" s="48"/>
-      <c r="Y17" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9566,29 +9528,38 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302A79DC-61FE-4A17-87F9-B836F0BDEDD0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048D6981-73D2-4F8C-88D7-D5FA77AC2EB0}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="43"/>
-      <c r="H1" s="41" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="49"/>
+      <c r="H1" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="43"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="49"/>
+    </row>
+    <row r="2" spans="1:13" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>24</v>
       </c>
@@ -9626,7 +9597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="F3" s="15"/>
       <c r="H3">
         <f>$F3</f>
@@ -9653,7 +9624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H4">
         <f t="shared" ref="H4:H28" si="0">$F4</f>
         <v>0</v>
@@ -9679,7 +9650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9705,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9731,7 +9702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H7">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9757,7 +9728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9783,7 +9754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9809,7 +9780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9835,7 +9806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H11">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9861,7 +9832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H12">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9887,7 +9858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9913,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9939,7 +9910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9965,7 +9936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="H16">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9991,7 +9962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H17">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10017,7 +9988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H18">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10043,7 +10014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H19">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10069,7 +10040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H20">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10095,7 +10066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10121,7 +10092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H22">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10147,7 +10118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10173,7 +10144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H24">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10199,7 +10170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10225,7 +10196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H26">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10251,7 +10222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H27">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10277,7 +10248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H28">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -10313,20 +10284,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c2b20bf0-79f3-4559-a8ab-bcb74dcd8cd8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10583,14 +10554,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE208467-E14A-4CB9-9FC8-72DFB8E94FF2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -10603,6 +10566,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="08a9f8ec-165a-4165-a8e9-ed45c2de7bcb"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D595912-0053-4104-933F-CDA3B3DBC546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
